--- a/www/download/COUNTRY.LUX.WIOD16.xlsx
+++ b/www/download/COUNTRY.LUX.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Luxemburgo</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.0833030754195</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.11606514762604</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1.05802227859658</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>0.884373370997593</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803957956125439</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.803863247279255</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>0.796453625882952</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.729631448483822</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.679885371678815</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>0.717040754328034</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.754409528394553</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.718465465074036</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>0.778335917583467</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>0.752858667912329</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>0.754544318108612</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.263</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.279</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.287</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.293</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.308</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.334</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.353</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>0.379</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.405</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.244</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.26</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.268</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.273</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.287</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.299</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.313</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.328</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.331</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0.337</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.347</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>0.356</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>0.366</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.381</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>421.127</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>442.933</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>454.953</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>462.588</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>472.922</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>478.116</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>496.314</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>521.989</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>546.799</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>534.89</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>546.02</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>561.799</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>572.337</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>585.278</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>610.41</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>391.961</t>
+          <t>428645578.163094</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>413.078</t>
+          <t>448410990.533151</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>424.934</t>
+          <t>440451099.200796</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>432.036</t>
+          <t>477765324.11535</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>441.649</t>
+          <t>519033115.389385</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>447.886</t>
+          <t>521556402.848561</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>466.147</t>
+          <t>559256164.658585</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>491.041</t>
+          <t>582657475.553029</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>514.935</t>
+          <t>659102315.799573</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>503.329</t>
+          <t>635871317.889415</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>513.946</t>
+          <t>706205088.579532</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>528.725</t>
+          <t>689700105.485118</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>538.872</t>
+          <t>683783052.25547</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>551.023</t>
+          <t>622268759.702016</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>575.236</t>
+          <t>641011501.009062</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>261355485.255603</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>272448218.335439</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>296066020.091404</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>314001918.574562</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>339315485.617356</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>367554157.842774</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>396705451.864302</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>374516107.035379</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>489490117.630874</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>542552703.149704</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>531971510.071077</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>562487989.439198</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>520436805.911152</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>530312851.99769</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>575849027.224523</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1062785.49401904</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1103304.15895378</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>965594.998620667</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>871058.667378378</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>782492.460199463</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>760321.320543764</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>715573.764081565</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>610662.061101575</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>739745.253401756</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>908369.654785457</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>928467.624564641</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>775634.540365703</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>903254.667765955</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>754168.323886951</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>743630.31846366</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1488.78954899653</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1518.68791639784</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1556.95227135137</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>1738.50867672795</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1970.14603697408</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2105.07571247687</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2285.50264408098</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2701.96947077254</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>3029.352161023</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>2654.42019017431</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>3006.75596951628</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>3277.09994751467</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>3225.84213450183</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>3242.01752749114</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3305.92164552696</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3482.90227780211</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3609.25723962152</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>3566.46636005606</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>4210.19687876538</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>5056.76557503083</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5455.73086480707</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6180.23693274446</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>7269.87277549434</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>8925.98567698761</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>7836.6529667163</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>9642.41248914173</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>10000.5984696416</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>9660.48754052097</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>8782.67536874226</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>9089.11958904991</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.49972364121865</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.516170678317366</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.435267714507765</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.375902421110238</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.301588105230318</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.218557838193709</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.175045610816186</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.311134530066055</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.0519824230410992</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.0722947336212627</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.0338843523192978</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.0600243739832741</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.0354225409876079</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.0390526986556985</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>-0.00106456240358321</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4002.77836802995</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4388.67803750515</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>4484.25212354587</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>5648.31433980146</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>6872.00064717984</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>7107.89849837285</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>7397.92431950002</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>8682.82239584366</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>10175.1355588096</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>9318.12266566179</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>10036.7329479272</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>11209.7777763731</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>11452.0343635971</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>12112.1571871676</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>12883.903814792</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0833030754195</t>
+          <t>1069.94508230893</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11606514762604</t>
+          <t>1047.35408578572</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05802227859658</t>
+          <t>1103.48870701232</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884373370997593</t>
+          <t>1148.63342200886</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803957956125439</t>
+          <t>1213.61810371385</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803863247279255</t>
+          <t>1279.47282292886</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796453625882952</t>
+          <t>1326.10881452215</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729631448483822</t>
+          <t>1197.03425395653</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679885371678815</t>
+          <t>1491.66575538892</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.717040754328034</t>
+          <t>1637.30181715214</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.754409528394553</t>
+          <t>1576.58559086918</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718465465074036</t>
+          <t>1618.76363945896</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778335917583467</t>
+          <t>1461.90114019987</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.752858667912329</t>
+          <t>1448.38819030341</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.754544318108612</t>
+          <t>1512.4468856031</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>883356792.827355</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>862502485.494194</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>946789212.295369</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>1054041125.53763</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1151477731.64936</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>1222972426.20377</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1577439665.53375</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>1724787081.14152</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1644237825.66357</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>1663367821.00128</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1663246732.90156</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>1692889159.86166</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1632846542.59291</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1896535069.16697</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1959562341.34016</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-21910803.1471571</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>-28145762.6114923</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>-31099252.9839751</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>-59464633.1764159</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>-32972098.0797744</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>-87759269.9104804</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>48527427.6081204</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>136694610.08546</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>126541421.735634</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>93033859.3142312</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>163769359.39735</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>52445878.2230046</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>-68711284.9826785</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>-96440855.1679071</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>-124358811.80902</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>905267595.974512</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>890648248.105686</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>977888465.279344</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>1113505758.71404</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>1184449829.72913</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>1310731696.11425</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1528912237.92563</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>1588092471.05606</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>1517696403.92793</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1570333961.68705</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1499477373.50421</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>1640443281.63865</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>1701557827.57559</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1992975924.33487</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>2083921153.14918</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1604.62193474434</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>1587.9675546842</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1583.8017144987</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>1580.40750631013</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1579.63088808613</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1559.1116371358</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>1558.23834196891</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1569.47294403426</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>1569.20615572147</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>1518.93351842351</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>1523.16400924664</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1521.59836537355</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>1513.68539325843</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.189</t>
+          <t>1504.9516578358</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>1510.83679151127</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1603.43891220751</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>1586.5499445209</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>1582.66711365162</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>1579.33912538038</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>1578.24924320508</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>1553.38521357594</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>1552.97112274977</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1564.24535404777</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1564.11516581589</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>1514.7536446155</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>1518.61934494476</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>1517.4736555841</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1509.64558366635</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>1501.17426415576</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>1507.1490626315</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>26495.8472647379</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>25932.9756968253</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>27389.7648759107</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>34106.4032764757</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>44264.1629844507</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>50494.0374161355</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>63486.9078723766</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>81441.5125229867</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>90609.8447068308</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>73252.0743282996</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>82727.6660909406</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>95685.1227514939</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>93767.5853199077</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>107359.516900761</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>118439.396739775</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>194877238.529796</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>202892051.423406</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>189024959.61203</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>206006235.253684</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>236096537.063317</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>233138106.290672</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>266544863.367935</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>271043729.158644</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>312675903.207877</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>277213975.954399</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>350864952.198153</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>338457508.517058</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>309300044.056028</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>265139664.247214</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>273877164.509769</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>22666.2026859574</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>22454.3242844799</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>23290.6791002017</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>29365.2587475248</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>38689.2844634355</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>44091.4424221417</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>53460.9334659647</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>68400.5300217386</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>77970.4128547073</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>61752.6467185166</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>69654.3728939984</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>81997.7185310179</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>81201.4510463915</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>91745.7688366877</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>102667.400373425</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>421.127</t>
+          <t>486550311.937776</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>442.933</t>
+          <t>508497618.132522</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>454.953</t>
+          <t>473911981.255757</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>462.588</t>
+          <t>538698415.414484</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>472.922</t>
+          <t>618268983.588867</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>478.116</t>
+          <t>648794083.682405</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>496.314</t>
+          <t>693333986.60097</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>521.989</t>
+          <t>720413578.416859</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>546.799</t>
+          <t>868766283.014041</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>534.89</t>
+          <t>821114353.767148</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>546.02</t>
+          <t>883496956.993414</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>561.799</t>
+          <t>908304411.27742</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>572.337</t>
+          <t>900048994.968079</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>585.278</t>
+          <t>859642666.942769</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>610.41</t>
+          <t>931050078.6078</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>391.961</t>
+          <t>3829.64457878048</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>413.078</t>
+          <t>3478.65141234544</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>424.934</t>
+          <t>4099.085775709</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>432.036</t>
+          <t>4741.14452895095</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>441.649</t>
+          <t>5574.87852101519</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>447.886</t>
+          <t>6402.59499399383</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>466.147</t>
+          <t>10025.974406412</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>491.041</t>
+          <t>13040.982501248</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>514.935</t>
+          <t>12639.4318521236</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>503.329</t>
+          <t>11499.4276097829</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>513.946</t>
+          <t>13073.2931969422</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>528.725</t>
+          <t>13687.404220476</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>538.872</t>
+          <t>12566.1342735162</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>551.023</t>
+          <t>15613.7480640728</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>575.236</t>
+          <t>15771.9963663502</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>428.739</t>
+          <t>-291673073.40798</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>448.488</t>
+          <t>-305605566.709116</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>440.588</t>
+          <t>-284887021.643727</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>477.912</t>
+          <t>-332692180.160801</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>519.177</t>
+          <t>-382172446.52555</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>521.483</t>
+          <t>-415655977.391733</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>559.275</t>
+          <t>-426789123.233035</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>583.017</t>
+          <t>-449369849.258215</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>659.208</t>
+          <t>-556090379.806165</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>635.932</t>
+          <t>-543900377.812749</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>706.406</t>
+          <t>-532632004.795261</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>690.143</t>
+          <t>-569846902.760362</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>683.93</t>
+          <t>-590748950.912051</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>622.339</t>
+          <t>-594503002.695555</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>640.824</t>
+          <t>-657172914.098031</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>5696.31115327104</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>5801.40819062729</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6406.62012936708</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>8035.99897897897</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>9416.91076058759</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>9605.50216727426</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>10206.6890499067</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>12763.2933984555</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13499.66256429</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>11663.8564635728</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12000.8690661478</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>13284.9827208009</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12548.7637561977</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>13288.7048901732</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>14118.2956227169</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>183.227</t>
+          <t>0.106529942211187</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>188.68</t>
+          <t>0.0781234934543135</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>192.28</t>
+          <t>0.0808464603179134</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>197.283</t>
+          <t>0.082440957426271</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>202.218</t>
+          <t>0.0786146949111721</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>201.241</t>
+          <t>0.0840711917809197</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>206.818</t>
+          <t>0.110346890665147</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>216.554</t>
+          <t>0.116583848594904</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>223.69</t>
+          <t>0.0938012481915682</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>215.381</t>
+          <t>0.0704953642002901</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>220.213</t>
+          <t>0.0838192792395475</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>226.008</t>
+          <t>0.0875333779890957</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>228.33</t>
+          <t>0.0753243189617928</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>229.703</t>
+          <t>0.0804405597605204</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>233.151</t>
+          <t>0.075068050086429</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>9654.43153718084</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>10358.7558690422</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>11739.1667788993</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>14467.4741478192</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>16890.1227632074</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>18057.4721744957</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>19786.9901805449</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>23563.7103941223</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>27228.7867830864</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>26515.1982463941</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>26185.3719234795</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>28867.6971003835</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>27726.8008429228</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>30593.4022807124</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>32684.9309206109</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>261.394</t>
+          <t>10208.9992739055</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>272.463</t>
+          <t>10947.1306257508</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>296.137</t>
+          <t>12401.4048085141</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>314.086</t>
+          <t>15287.7454972193</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>339.314</t>
+          <t>17857.8729085335</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>367.543</t>
+          <t>19085.0392471106</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>396.722</t>
+          <t>20878.9548187799</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>374.642</t>
+          <t>24844.0556418033</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>489.54</t>
+          <t>28753.0785338397</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>542.595</t>
+          <t>28028.1978106935</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>532.045</t>
+          <t>27692.0707537294</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>562.602</t>
+          <t>30546.0282507805</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>520.471</t>
+          <t>29326.5081458503</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>530.325</t>
+          <t>32364.8782574298</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>575.75</t>
+          <t>34599.2278903424</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>49.95</t>
+          <t>44399.6581512182</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>51.61</t>
+          <t>46815.6370370695</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>43.49</t>
+          <t>52233.315591562</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>65337.5964640435</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>30.16</t>
+          <t>76299.024647537</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>21.86</t>
+          <t>80867.7530151146</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>86177.7192967943</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>100766.449641372</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>116367.833799383</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-7.24</t>
+          <t>115267.432635396</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-3.4</t>
+          <t>114250.808400574</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>127542.610285798</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>125418.102444949</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>136161.243830329</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>143361.754943028</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.063</t>
+          <t>14897.9011193249</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.104</t>
+          <t>16317.8259681201</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>16983.7926699464</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>16594.3024053247</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>16900.5312943182</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>17187.9472939774</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.716</t>
+          <t>17361.2526890662</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>18727.1360272197</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>19321.1073048528</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>19394.80712281</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>19292.8175989607</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>19113.6052104039</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>19363.8950145017</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>20291.0999385194</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>21482.0899913769</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>14033.0910837521</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>15422.7646221308</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>16071.2066485853</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>15730.5036978144</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>16015.0079193029</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>16288.8724532516</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>16455.1534799143</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>17786.295681739</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>18328.661356725</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>18371.1669095908</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>18243.1582740333</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>18065.2069985313</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>18307.2392968089</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>19204.0973368407</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>20310.3375573873</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>8732.67138507569</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8046.07915113017</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8707.13079979213</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>11034.8083482285</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>12870.225191866</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>13906.5468709986</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>16907.3676885152</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>20430.5629042793</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>21090.5836185407</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>17443.9423097265</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>19613.1533605989</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>22374.0132922357</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>20899.0675157432</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>23065.043858568</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>23645.7912153336</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>391961000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>413078000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>424934000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>432036000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>441649000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>447886000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>466147000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>491041000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>514935000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>503329000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>513946000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>528725000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>538872000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>551023000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>575236000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>421127195.902182</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>442933013.511344</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>454953488.490295</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>462588429.823914</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>472922385.726402</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>478116434.88654</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>496314041.1196</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>521988674.645739</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>546799020.817577</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>534889806.986626</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>546019585.474889</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>561799096.770344</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>572336833.679586</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>585277822.109048</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>610410441.856384</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>183227379.378413</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>188680470.160696</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>192280332.992993</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>197282736.492324</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>202218398.335872</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>201240813.289666</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>206817547.119214</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>216554368.897416</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>223689920.302062</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>215381448.142096</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>220213185.04891</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>226008092.050431</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>228329695.739664</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>229702925.482604</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>233150612.163868</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>262640</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>279180</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>287460</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>292900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>299650</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>307790</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>319590</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>333700</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>349590</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>353120</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>359550</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>370220</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>379120</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>389880</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>405010</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>244270</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>260130</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>268300</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>273370</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>279590</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>287270</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>299150</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>312870</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>328150</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>331370</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>337420</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>347480</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>356000</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>366140</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>380740</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>421127195.902182</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>442933013.511344</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>454953488.490295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>462588429.823914</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>472922385.726402</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>478116434.88654</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>496314041.1196</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>521988674.645739</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>546799020.817577</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>534889806.986626</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>546019585.474889</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>561799096.770344</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>572336833.679586</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>585277822.109048</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>610410441.856384</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>391961000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>413078000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>424934000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>432036000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>441649000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>447886000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>466147000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>491041000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>514935000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>503329000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>513946000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>528725000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>538872000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>551023000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>575236000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>50505.3760674947</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50980.8963623003</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>55018.97952</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>68137.86924379</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>84902.9774229963</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>96571.2292327918</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>117965.874572581</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>147783.756</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>162520.16424</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>138028.710634105</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>152441.88981628</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>172104.974100951</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>167672.226133539</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>189168.449694447</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>211968.19051659</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18941.9002274947</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18993.3780823003</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>21108.43968</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>26322.26940379</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>30728.2714529963</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>32991.4987327918</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>37786.2720125805</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>45274.7416</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>49843.49996</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>45472.1537941048</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>47305.2627662803</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>52919.8461009505</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>50225.8315735393</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>55429.7093644472</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>58245.3736021142</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>58450.966053208</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>62762.3644904813</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>65397.8811030637</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>67279.1529328455</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>69169.3211737415</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>69939.7602689137</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>71011.4269700638</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>73375.0413327473</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>76511.9841507789</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>79066.9185999762</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>79593.0875015059</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>81951.619991616</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>85652.846177443</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>88786.8986500365</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>92709.4134564269</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
